--- a/output/2026-09-12_19_Croazia_Karlovacka_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-09-12_19_Croazia_Karlovacka_Componentistica_Ventilazione_industriale.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
